--- a/outputs/evaluation/architecture/validation/gemini-3-5/CF_M01/run_3/CF_M01_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/gemini-3-5/CF_M01/run_3/CF_M01_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.75</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.7059</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.7188</v>
       </c>
       <c r="D3" t="n">
+        <v>0.6765</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9702</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.875</v>
       </c>
       <c r="D4" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8935999999999999</v>
       </c>
     </row>
@@ -1224,13 +1238,11 @@
           <t>['AU_11']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>AWS RDS</t>
@@ -1254,13 +1266,11 @@
           <t>CF_M01_AU15</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M01_AU35</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1306,13 +1316,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Waapiti Mobile Platform</t>
@@ -1336,13 +1344,11 @@
           <t>CF_M01_AU05</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M01_AU09</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1388,13 +1394,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Core Service</t>
@@ -1418,13 +1422,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M01_AU11</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1445,7 +1447,6 @@
       <c r="D5" t="n">
         <v>0.8734</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1466,7 +1467,6 @@
           <t>['AU_07', 'AU_11', 'AU_12']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_38</t>
@@ -1477,7 +1477,6 @@
           <t>core, base de dades, conjunt de serveis cloud aws</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1496,7 +1495,6 @@
           <t>CF_M01_AU11, CF_M01_AU15, CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M01_AU37</t>
@@ -1527,7 +1525,6 @@
       <c r="D6" t="n">
         <v>0.8747</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1548,7 +1545,6 @@
           <t>['AU_06', 'AU_07', 'AU_08']</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_37</t>
@@ -1559,7 +1555,6 @@
           <t>api gateway, core, mòdul analític</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1578,7 +1573,6 @@
           <t>CF_M01_AU10, CF_M01_AU11, CF_M01_AU12</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M01_AU26</t>
@@ -1609,7 +1603,6 @@
       <c r="D7" t="n">
         <v>0.8787</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1630,7 +1623,6 @@
           <t>['AU_09', 'AU_33']</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_40</t>
@@ -1641,7 +1633,6 @@
           <t>api player, player</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1660,7 +1651,6 @@
           <t>CF_M01_AU27, CF_M01_AU13</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M01_AU28</t>
@@ -1691,7 +1681,6 @@
       <c r="D8" t="n">
         <v>0.8801</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1712,7 +1701,6 @@
           <t>['AU_02', 'AU_06']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_35</t>
@@ -1723,7 +1711,6 @@
           <t>capa de presentació, api gateway</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1742,7 +1729,6 @@
           <t>CF_M01_AU05, CF_M01_AU10</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M01_AU25</t>
@@ -1773,7 +1759,6 @@
       <c r="D9" t="n">
         <v>0.896</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1794,7 +1779,6 @@
           <t>['AU_08', 'AU_12', 'AU_11']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_39</t>
@@ -1805,7 +1789,6 @@
           <t>mòdul analític, conjunt de serveis cloud aws, base de dades</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1824,7 +1807,6 @@
           <t>CF_M01_AU12, CF_M01_AU16, CF_M01_AU15</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M01_AU36</t>
@@ -1880,13 +1862,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>AWS cloud services set</t>
@@ -1912,13 +1892,11 @@
           <t>CF_M01_AU07</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1964,13 +1942,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>API Gateway Service</t>
@@ -1994,13 +1970,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M01_AU10</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2021,7 +1995,6 @@
       <c r="D12" t="n">
         <v>0.9256</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -2042,7 +2015,6 @@
           <t>['AU_02', 'AU_03']</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_34</t>
@@ -2053,7 +2025,6 @@
           <t>capa de presentació, capa de negoci</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -2072,7 +2043,6 @@
           <t>CF_M01_AU01, CF_M01_AU02</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M01_AU24</t>
@@ -2103,7 +2073,6 @@
       <c r="D13" t="n">
         <v>0.9268999999999999</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -2124,7 +2093,6 @@
           <t>['AU_10', 'AU_33']</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_41</t>
@@ -2135,7 +2103,6 @@
           <t>web socket, player</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -2154,7 +2121,6 @@
           <t>CF_M01_AU27, CF_M01_AU14</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M01_AU29</t>
@@ -2210,13 +2176,11 @@
           <t>['AU_12']</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Amazon DynamoDB</t>
@@ -2240,13 +2204,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M01_AU18</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2287,7 +2249,6 @@
           <t>43</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
@@ -2298,7 +2259,6 @@
           <t>P_03</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>API Gateway</t>
@@ -2322,13 +2282,11 @@
           <t>CF_M01_P03</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M01_P04</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2374,13 +2332,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Api Player</t>
@@ -2404,13 +2360,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M01_AU13</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2456,13 +2410,11 @@
           <t>['AU_11']</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>MySQL</t>
@@ -2486,13 +2438,11 @@
           <t>CF_M01_AU15</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M01_AU32</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2533,14 +2483,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_33</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Player</t>
@@ -2559,14 +2506,11 @@
       <c r="P18" t="n">
         <v>8</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M01_AU27</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2607,14 +2551,11 @@
           <t>49</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_20</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Amazon Athena</t>
@@ -2638,13 +2579,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M01_AU20</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2690,13 +2629,11 @@
           <t>['AU_34', 'AU_35']</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_31</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2720,13 +2657,11 @@
           <t>CF_M01_AU24, CF_M01_AU25</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M01_AU03</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2767,14 +2702,11 @@
           <t>46</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>NestJS</t>
@@ -2798,13 +2730,11 @@
           <t>CF_M01_AU02</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M01_AU33</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2845,14 +2775,11 @@
           <t>40</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Client</t>
@@ -2876,13 +2803,11 @@
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M01_AU01</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2928,13 +2853,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Web Socket</t>
@@ -2958,13 +2881,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M01_AU14</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3010,13 +2931,11 @@
           <t>['AU_12']</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Amazon S3</t>
@@ -3040,13 +2959,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M01_AU17</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3087,14 +3004,11 @@
           <t>49</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>AU_21</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>AWS Glue</t>
@@ -3118,13 +3032,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>CF_M01_AU21</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3170,13 +3082,11 @@
           <t>['P_01']</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Three Layers</t>
@@ -3200,13 +3110,11 @@
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>CF_M01_P02</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3247,14 +3155,11 @@
           <t>50</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>AU_22</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Kinesis Data Streams</t>
@@ -3280,13 +3185,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>CF_M01_AU22</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3327,14 +3230,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Client-Server</t>
@@ -3353,14 +3253,11 @@
       <c r="P28" t="n">
         <v>41</v>
       </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3401,14 +3298,11 @@
           <t>46</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>AU_18</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>TypeScript</t>
@@ -3432,13 +3326,11 @@
           <t>CF_M01_AU33</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>CF_M01_AU34</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3479,14 +3371,11 @@
           <t>51</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>AU_23</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>Kinesis Data Firehose</t>
@@ -3510,13 +3399,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>CF_M01_AU23</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3562,13 +3449,11 @@
           <t>['AU_36']</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>AU_32</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>TCP</t>
@@ -3592,13 +3477,11 @@
           <t>CF_M01_AU26</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
           <t>CF_M01_AU31</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3672,7 +3555,6 @@
           <t>Capa de presentació</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Capa de presentació: És la capa que s’encarrega de mostrar la informació à l’usuari.</t>
@@ -3708,7 +3590,6 @@
           <t>Capa de negoci</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Capa de negoci: Aquesta capa és el nucli de l’aplicació, que s’encarrega de processar tota la informació.</t>
@@ -3744,7 +3625,6 @@
           <t>Capa de dades</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Capa de dades: És la capa que s’encarrega d'emmagatzemar totes les dades.</t>
@@ -3780,7 +3660,6 @@
           <t>Mòdul analític</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>El mòdul analític té com a funció principal obtenir i processar les dades dels playlogs, les connexions i les accions en plataforma.</t>
@@ -3816,7 +3695,6 @@
           <t>Base de dades</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>La base de dades utilitzada és una base de dades MySQL que s’encarrega d’emmagatzemar totes les dades necessàries per al funcionament del sistema.</t>
@@ -3852,7 +3730,6 @@
           <t>Infraestructura AWS</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>És el conjunt de serveis de computació en el núvol que permet la creació d’aplicacions escalables i altament disponibles.</t>
@@ -3888,7 +3765,6 @@
           <t>AWS Cloud Development</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Per poder desenvolupar tota la infraestructura necessària per al projecte s’ha fet ús de l’AWS Cloud Development, també anomenat AWS CDK.</t>
@@ -3924,7 +3800,6 @@
           <t>AWS CloudFormation</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>AWS CloudFormation és un servei d’Amazon que ajuda a configurar els recursos d’AWS.</t>
@@ -3960,7 +3835,6 @@
           <t>NodeJS</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Aquest framework és un framework de NodeJS que té com a funció principal la creació d’aplicacions de backend.</t>
@@ -3996,7 +3870,6 @@
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Aquest llenguatge de programació que està construït a un nivell superior de JavaScript, és a dir, que estén la sintaxi de JavaScript.</t>
@@ -4032,7 +3905,6 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Com es pot veure en la figura 11.5 permet fer ús dels llenguatges de programació TypeScript, JavaScript, Python, Java i C#/.NET</t>
@@ -4068,7 +3940,6 @@
           <t>Java</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Com es pot veure en la figura 11.5 permet fer ús dels llenguatges de programació TypeScript, JavaScript, Python, Java i C#/.NET</t>
@@ -4104,7 +3975,6 @@
           <t>C#/.NET</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Com es pot veure en la figura 11.5 permet fer ús dels llenguatges de programació TypeScript, JavaScript, Python, Java i C#/.NET</t>
@@ -4135,7 +4005,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>api gateway, core, mòdul analític, api player, web socket</t>
@@ -4151,7 +4020,6 @@
           <t>CF_M01_AU24</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>0.7455000000000001</v>
       </c>
@@ -4167,7 +4035,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>web socket, base de dades, conjunt de serveis cloud aws</t>
@@ -4183,7 +4050,6 @@
           <t>CF_M01_AU28</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>0.7483</v>
       </c>
@@ -4260,7 +4126,6 @@
           <t>Server</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>The server is the software that is responsible for processing user requests.</t>
@@ -4296,7 +4161,6 @@
           <t>REST</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
@@ -4307,7 +4171,6 @@
           <t>AU_37</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>0.6819</v>
       </c>
@@ -4328,7 +4191,6 @@
           <t>Presentation Layer</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>It is the layer that is responsible for displaying information to the user. In this project, it is the visual interface of the Waapiti platform.</t>
@@ -4339,7 +4201,6 @@
           <t>AU_35</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>0.7413999999999999</v>
       </c>
@@ -4360,7 +4221,6 @@
           <t>Business Layer</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>This layer is the core of the application, which is responsible for processing all the information. In our context, it is the software that is responsible for processing user requests.</t>
@@ -4396,7 +4256,6 @@
           <t>Data Layer</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>It is the layer that is responsible for storing all the data. In our case, it would be the database and AWS storage services.</t>
@@ -4432,7 +4291,6 @@
           <t>Web platform interface</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
@@ -4463,7 +4321,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>presentation layer, business layer</t>
@@ -4479,7 +4336,6 @@
           <t>AU_35</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>0.7702</v>
       </c>
@@ -4500,7 +4356,6 @@
           <t>Analytical module</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
@@ -4536,7 +4391,6 @@
           <t>SQL database</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. [...] The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system. This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
@@ -4572,7 +4426,6 @@
           <t>Service-oriented</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Both the business layer and the data layer are divided into several different services</t>
